--- a/DataTables/DetailText/剧情/000_07名望过低.xlsx
+++ b/DataTables/DetailText/剧情/000_07名望过低.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889C570A-5F54-45AC-BC12-D381A4971C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDCF6BB-DEEC-4FE1-99AC-E213E997501C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -830,7 +830,7 @@
         <v>40</v>
       </c>
       <c r="H2" s="1">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="I2" s="21"/>
       <c r="J2" s="21"/>
